--- a/public/documents/pieces-reponse-1/R1-cascade-nature-des-chiffres.xlsx
+++ b/public/documents/pieces-reponse-1/R1-cascade-nature-des-chiffres.xlsx
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>5272.8</v>
+        <v>5457.3</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>49.64</v>
+        <v>51.38</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1699.32 L versés à la main sur 4091.05 L versés toutes formes confondues</t>
+          <t>1653.19 L versés à la main sur 4275.55 L versés toutes formes confondues</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>493.92</v>
+        <v>483.03</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>4.65</v>
+        <v>4.55</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
       <c r="E14" s="3" t="inlineStr"/>
       <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" s="3" t="n">
-        <v>8393.92</v>
+        <v>8567.530000000001</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>79.02</v>
+        <v>80.66</v>
       </c>
       <c r="I14" s="3" t="inlineStr"/>
     </row>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2228.08</v>
+        <v>2054.47</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>20.98</v>
+        <v>19.34</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5611.77</v>
+        <v>5796.27</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>52.83</v>
+        <v>54.57</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>771.39</v>
+        <v>760.5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>7.26</v>
+        <v>7.16</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2228.08</v>
+        <v>2054.47</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>20.98</v>
+        <v>19.34</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>7622.53</v>
+        <v>7807.03</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>71.77</v>
+        <v>73.5</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
@@ -1404,17 +1404,17 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>29.1 % du volume versé à la main</t>
+          <t>29.2 % du volume versé à la main</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Résultat des taux ci-dessus appliqués à l’assiette de 1699.32 L versée à la main</t>
+          <t>Résultat des taux ci-dessus appliqués à l’assiette de 1653.19 L versée à la main</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Soit 12.1 % du volume versé toutes formes confondues et 4.6 % des achats</t>
+          <t>Soit 11.3 % du volume versé toutes formes confondues et 4.5 % des achats</t>
         </is>
       </c>
     </row>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5272.8</v>
+        <v>5457.3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5272.77</v>
+        <v>5457.27</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>493.92</v>
+        <v>483.03</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>493.92</v>
+        <v>483.03</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>8393.92</v>
+        <v>8567.530000000001</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>8393.92</v>
+        <v>8567.530000000001</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>7622.53</v>
+        <v>7807.03</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>7622.53</v>
+        <v>7807.03</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
